--- a/artfynd/A 24904-2026 artfynd.xlsx
+++ b/artfynd/A 24904-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92594062</v>
+        <v>60330393</v>
       </c>
       <c r="B2" t="n">
-        <v>97602</v>
+        <v>98053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Höstlåsbräken</t>
+          <t>Topplåsbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Botrychium multifidum</t>
+          <t>Botrychium lanceolatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Rupr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(S. G. Gmel.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flaten, Långsjön NV 350 m kontroll, Gstr</t>
+          <t>Flaten, Lisselsjön SSO, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617365</v>
+        <v>617384</v>
       </c>
       <c r="R2" t="n">
-        <v>6706057</v>
+        <v>6706159</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -738,19 +747,24 @@
           <t>Hedesunda</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>XG-Gäv-0081</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-08-31</t>
+          <t>2009-07-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-08-31</t>
+          <t>2009-07-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>48 fert + 116 veg ex. Längst norrut utmed vägen 14 fert ex+30 veg ex, längre söderut utmed vägen 34 fert + veg 86 ex.</t>
+          <t>1 snyggt ex  Inv med AnnKristin Jäderström.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,12 +778,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kulturmark, skogsväg, i mittsträngen, mest med plantor på   västra sidan, mindre på östra sidan om mittsträng</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 314748H</t>
+          <t>Kulturmark, skogsväg                                        örtrik men ganska lucker ängsveg av klöver smultrontyp</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -780,26 +789,21 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Ståhl, Birgitta Hellström</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Gästriklands flora (2016)</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119734414</v>
+        <v>86543644</v>
       </c>
       <c r="B3" t="n">
-        <v>96963</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,26 +811,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222112</v>
+        <v>167</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,19 +838,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lisselsjön SO, vändplanen, Gstr</t>
+          <t>Långsjön NV 400 m, skogsväg (höstlåsb), Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617382</v>
+        <v>617383</v>
       </c>
       <c r="R3" t="n">
-        <v>6706144</v>
+        <v>6705957</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,19 +872,24 @@
           <t>Hedesunda</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>XG-Gäv-0073</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2009-07-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2009-07-18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gulnat ex på väg att vissna ner</t>
+          <t>115 (86 veg+29 fert) läckar med uppehåll knappt 500 m. sydligast 1573149/6706728. Småvuxen, verkar under etablering "groddplantor". Svårinventerad - knäböj. Inv med AnnKristin Jäderström. Lokalen förstörd av virkestransporter senare.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +898,488 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kulturmark, grässträng, 1 m bred i skogsväg, mager          gräsmark, mest mest glesveg, mossa i bottenskiktet</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>91235037</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98056</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>167</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Höstlåsbräken</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Botrychium multifidum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(S. G. Gmel.) Rupr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långsjön NV 350 m, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>617383</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6706130</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2013-09-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2013-09-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kulturmark, skogsväg i mittsträngen</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 314359N</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>92592429</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98056</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>167</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Höstlåsbräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Botrychium multifidum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(S. G. Gmel.) Rupr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flaten, Långsjön NV 350 m kontroll, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>617365</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6706057</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-08-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-08-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>48 fert + 116 veg ex. Längst norrut utmed vägen 14 fert ex+30 veg ex, längre söderut utmed vägen 34 fert + veg 86 ex.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kulturmark, skogsväg, i mittsträngen, mest med plantor på   västra sidan, mindre på östra sidan om mittsträng</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 314748H</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Peter Ståhl, Birgitta Hellström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>91262192</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flaten, Långsjön NV 350 m, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>617383</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6705957</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2009-07-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2009-07-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>fläckar med uppehåll knappt 500 m. sydligast 1573149/6706728. Småvuxen, verkar under etablering groddplantorSvårinventerad - knäböj. Inv med AnnKristin Jäderström. lokalenförstörd av virkestransporter senare.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kulturmark, grässträng, 1 m bred i skogsväg, mager          gräsmark, mest mest glesveg, mossa i bottenskiktet</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 308387H</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119734414</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lisselsjön SO, vändplanen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>617382</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6706144</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gulnat ex på väg att vissna ner</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Inger Carlsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Inger Carlsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24904-2026 artfynd.xlsx
+++ b/artfynd/A 24904-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60330393</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86543644</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91235037</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,6 +1169,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92592429</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91262192</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1380,8 +1410,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119734414</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>